--- a/backend/data/financials_by_company/1145.HK.xlsx
+++ b/backend/data/financials_by_company/1145.HK.xlsx
@@ -637,7 +637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -646,129 +646,127 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3724000</v>
+        <v>-941000</v>
       </c>
       <c r="E2" t="n">
-        <v>197000</v>
+        <v>13372000</v>
       </c>
       <c r="F2" t="n">
-        <v>197000</v>
+        <v>13372000</v>
       </c>
       <c r="G2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="H2" t="n">
-        <v>2195000</v>
+        <v>1496000</v>
       </c>
       <c r="I2" t="n">
-        <v>6040000</v>
+        <v>4925000</v>
       </c>
       <c r="J2" t="n">
-        <v>3921000</v>
+        <v>12431000</v>
       </c>
       <c r="K2" t="n">
-        <v>1726000</v>
+        <v>10935000</v>
       </c>
       <c r="L2" t="n">
-        <v>-20000</v>
+        <v>-447000</v>
       </c>
       <c r="M2" t="n">
-        <v>20000</v>
+        <v>447000</v>
       </c>
       <c r="N2" t="n">
-        <v>1509000</v>
+        <v>-2884000</v>
       </c>
       <c r="O2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="P2" t="n">
-        <v>8765000</v>
+        <v>11808000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1097704000</v>
+        <v>1092753000</v>
       </c>
       <c r="R2" t="n">
-        <v>1097704000</v>
+        <v>1092753000</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0016</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0016</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="V2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1111000</v>
+        <v>82000</v>
       </c>
       <c r="AD2" t="n">
-        <v>197000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-106000</v>
-      </c>
+        <v>13430000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-91000</v>
+        <v>-13430000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-20000</v>
+        <v>-447000</v>
       </c>
       <c r="AH2" t="n">
-        <v>20000</v>
+        <v>447000</v>
       </c>
       <c r="AI2" t="n">
-        <v>418000</v>
+        <v>-2070000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2725000</v>
+        <v>6883000</v>
       </c>
       <c r="AK2" t="n">
-        <v>389000</v>
+        <v>5360000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2336000</v>
+        <v>1523000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2336000</v>
+        <v>1523000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3143000</v>
+        <v>4813000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6040000</v>
+        <v>4925000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9183000</v>
+        <v>9738000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9183000</v>
+        <v>9738000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -777,43 +775,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1505000</v>
+        <v>4552000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3150000</v>
+        <v>-791000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3150000</v>
+        <v>-791000</v>
       </c>
       <c r="G3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="H3" t="n">
-        <v>2142000</v>
+        <v>2292000</v>
       </c>
       <c r="I3" t="n">
-        <v>6219000</v>
+        <v>7000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1645000</v>
+        <v>3761000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3787000</v>
+        <v>1469000</v>
       </c>
       <c r="L3" t="n">
-        <v>-187000</v>
+        <v>-346000</v>
       </c>
       <c r="M3" t="n">
-        <v>187000</v>
+        <v>346000</v>
       </c>
       <c r="N3" t="n">
-        <v>-824000</v>
+        <v>1914000</v>
       </c>
       <c r="O3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="P3" t="n">
-        <v>9032000</v>
+        <v>9828000</v>
       </c>
       <c r="Q3" t="n">
         <v>1097704000</v>
@@ -822,84 +820,82 @@
         <v>1097704000</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0036</v>
+        <v>0.001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0036</v>
+        <v>0.001</v>
       </c>
       <c r="U3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="V3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
       <c r="AC3" t="n">
-        <v>672000</v>
+        <v>661000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3150000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2100000</v>
-      </c>
+        <v>-797000</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>1050000</v>
+        <v>797000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-187000</v>
+        <v>-346000</v>
       </c>
       <c r="AH3" t="n">
-        <v>187000</v>
+        <v>346000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-520000</v>
+        <v>2544000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2813000</v>
+        <v>2828000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1250000</v>
+        <v>1493000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1563000</v>
+        <v>1335000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1563000</v>
+        <v>1335000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2293000</v>
+        <v>5372000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6219000</v>
+        <v>7000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8512000</v>
+        <v>12372000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8512000</v>
+        <v>12372000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -908,43 +904,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4552000</v>
+        <v>1505000</v>
       </c>
       <c r="E4" t="n">
-        <v>-791000</v>
+        <v>-3150000</v>
       </c>
       <c r="F4" t="n">
-        <v>-791000</v>
+        <v>-3150000</v>
       </c>
       <c r="G4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="H4" t="n">
-        <v>2292000</v>
+        <v>2142000</v>
       </c>
       <c r="I4" t="n">
-        <v>7000000</v>
+        <v>6219000</v>
       </c>
       <c r="J4" t="n">
-        <v>3761000</v>
+        <v>-1645000</v>
       </c>
       <c r="K4" t="n">
-        <v>1469000</v>
+        <v>-3787000</v>
       </c>
       <c r="L4" t="n">
-        <v>-346000</v>
+        <v>-187000</v>
       </c>
       <c r="M4" t="n">
-        <v>346000</v>
+        <v>187000</v>
       </c>
       <c r="N4" t="n">
-        <v>1914000</v>
+        <v>-824000</v>
       </c>
       <c r="O4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="P4" t="n">
-        <v>9828000</v>
+        <v>9032000</v>
       </c>
       <c r="Q4" t="n">
         <v>1097704000</v>
@@ -953,82 +949,84 @@
         <v>1097704000</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001</v>
+        <v>-0.0036</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001</v>
+        <v>-0.0036</v>
       </c>
       <c r="U4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="V4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
       <c r="AC4" t="n">
-        <v>661000</v>
+        <v>672000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-797000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>-3150000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2100000</v>
+      </c>
       <c r="AF4" t="n">
-        <v>797000</v>
+        <v>1050000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-346000</v>
+        <v>-187000</v>
       </c>
       <c r="AH4" t="n">
-        <v>346000</v>
+        <v>187000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2544000</v>
+        <v>-520000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2828000</v>
+        <v>2813000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1493000</v>
+        <v>1250000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1335000</v>
+        <v>1563000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1335000</v>
+        <v>1563000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5372000</v>
+        <v>2293000</v>
       </c>
       <c r="AO4" t="n">
-        <v>7000000</v>
+        <v>6219000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12372000</v>
+        <v>8512000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12372000</v>
+        <v>8512000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1037,122 +1035,124 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-941000</v>
+        <v>3724000</v>
       </c>
       <c r="E5" t="n">
-        <v>13372000</v>
+        <v>197000</v>
       </c>
       <c r="F5" t="n">
-        <v>13372000</v>
+        <v>197000</v>
       </c>
       <c r="G5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="H5" t="n">
-        <v>1496000</v>
+        <v>2195000</v>
       </c>
       <c r="I5" t="n">
-        <v>4925000</v>
+        <v>6040000</v>
       </c>
       <c r="J5" t="n">
-        <v>12431000</v>
+        <v>3921000</v>
       </c>
       <c r="K5" t="n">
-        <v>10935000</v>
+        <v>1726000</v>
       </c>
       <c r="L5" t="n">
-        <v>-447000</v>
+        <v>-20000</v>
       </c>
       <c r="M5" t="n">
-        <v>447000</v>
+        <v>20000</v>
       </c>
       <c r="N5" t="n">
-        <v>-2884000</v>
+        <v>1509000</v>
       </c>
       <c r="O5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="P5" t="n">
-        <v>11808000</v>
+        <v>8765000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1092753000</v>
+        <v>1097704000</v>
       </c>
       <c r="R5" t="n">
-        <v>1092753000</v>
+        <v>1097704000</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0016</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0016</v>
       </c>
       <c r="U5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="V5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="Z5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
       <c r="AC5" t="n">
-        <v>82000</v>
+        <v>1111000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13430000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>197000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-106000</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-13430000</v>
+        <v>-91000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-447000</v>
+        <v>-20000</v>
       </c>
       <c r="AH5" t="n">
-        <v>447000</v>
+        <v>20000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2070000</v>
+        <v>418000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6883000</v>
+        <v>2725000</v>
       </c>
       <c r="AK5" t="n">
-        <v>5360000</v>
+        <v>389000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1523000</v>
+        <v>2336000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1523000</v>
+        <v>2336000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4813000</v>
+        <v>3143000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4925000</v>
+        <v>6040000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9738000</v>
+        <v>9183000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9738000</v>
+        <v>9183000</v>
       </c>
     </row>
   </sheetData>
@@ -1458,47 +1458,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1097703568</v>
+        <v>1097704000</v>
       </c>
       <c r="C2" t="n">
-        <v>1097703568</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>1097704000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2146000</v>
+      </c>
       <c r="E2" t="n">
-        <v>9000</v>
+        <v>9938000</v>
       </c>
       <c r="F2" t="n">
-        <v>58804000</v>
+        <v>61452000</v>
       </c>
       <c r="G2" t="n">
-        <v>58804000</v>
+        <v>71238000</v>
       </c>
       <c r="H2" t="n">
-        <v>18657000</v>
+        <v>7748000</v>
       </c>
       <c r="I2" t="n">
-        <v>58804000</v>
+        <v>61452000</v>
       </c>
       <c r="J2" t="n">
-        <v>9000</v>
+        <v>152000</v>
       </c>
       <c r="K2" t="n">
-        <v>58804000</v>
+        <v>61452000</v>
       </c>
       <c r="L2" t="n">
-        <v>58804000</v>
+        <v>66330000</v>
       </c>
       <c r="M2" t="n">
-        <v>58804000</v>
+        <v>61452000</v>
       </c>
       <c r="N2" t="n">
-        <v>58804000</v>
+        <v>61452000</v>
       </c>
       <c r="O2" t="n">
-        <v>8605000</v>
+        <v>8219000</v>
       </c>
       <c r="P2" t="n">
         <v>49101000</v>
@@ -1510,103 +1512,125 @@
         <v>1098000</v>
       </c>
       <c r="S2" t="n">
-        <v>1003000</v>
+        <v>10999000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>5625000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>735000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>735000</v>
+      </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4890000</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4878000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>1003000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>150000</v>
-      </c>
+        <v>5374000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>9000</v>
+        <v>5048000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9000</v>
+        <v>140000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>4908000</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>311000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>59807000</v>
+        <v>72451000</v>
       </c>
       <c r="AI2" t="n">
-        <v>40147000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>59329000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>195000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>2731000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2731000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2731000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5167000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5167000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8756000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>40147000</v>
+        <v>42675000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-18339000</v>
+        <v>-23739000</v>
       </c>
       <c r="AS2" t="n">
-        <v>58486000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>66414000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>195000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>5753000</v>
+        <v>2025000</v>
       </c>
       <c r="AV2" t="n">
-        <v>52705000</v>
+        <v>64118000</v>
       </c>
       <c r="AW2" t="n">
-        <v>28000</v>
+        <v>76000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>19660000</v>
+        <v>13122000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>154000</v>
+        <v>276000</v>
       </c>
       <c r="BA2" t="n">
-        <v>568000</v>
+        <v>1392000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>18938000</v>
+        <v>11454000</v>
       </c>
       <c r="BD2" t="n">
-        <v>14681000</v>
+        <v>3814000</v>
       </c>
       <c r="BE2" t="n">
-        <v>4257000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>7640000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7640000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1097703568</v>
@@ -1614,39 +1638,41 @@
       <c r="C3" t="n">
         <v>1097703568</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>677000</v>
+      </c>
       <c r="E3" t="n">
-        <v>864000</v>
+        <v>2890000</v>
       </c>
       <c r="F3" t="n">
-        <v>57098000</v>
+        <v>61138000</v>
       </c>
       <c r="G3" t="n">
-        <v>57854000</v>
+        <v>64016000</v>
       </c>
       <c r="H3" t="n">
-        <v>16880000</v>
+        <v>14451000</v>
       </c>
       <c r="I3" t="n">
-        <v>57098000</v>
+        <v>61138000</v>
       </c>
       <c r="J3" t="n">
-        <v>108000</v>
+        <v>12000</v>
       </c>
       <c r="K3" t="n">
-        <v>57098000</v>
+        <v>61138000</v>
       </c>
       <c r="L3" t="n">
-        <v>57098000</v>
+        <v>61894000</v>
       </c>
       <c r="M3" t="n">
-        <v>57098000</v>
+        <v>61138000</v>
       </c>
       <c r="N3" t="n">
-        <v>57098000</v>
+        <v>61138000</v>
       </c>
       <c r="O3" t="n">
-        <v>6899000</v>
+        <v>9342000</v>
       </c>
       <c r="P3" t="n">
         <v>49101000</v>
@@ -1658,111 +1684,117 @@
         <v>1098000</v>
       </c>
       <c r="S3" t="n">
-        <v>1936000</v>
+        <v>5317000</v>
       </c>
       <c r="T3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>1491000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>735000</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>9000</v>
+        <v>756000</v>
       </c>
       <c r="X3" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>756000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1927000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>735000</v>
-      </c>
+        <v>3826000</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>855000</v>
+        <v>2134000</v>
       </c>
       <c r="AC3" t="n">
-        <v>99000</v>
+        <v>12000</v>
       </c>
       <c r="AD3" t="n">
-        <v>756000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>2122000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>821000</v>
+      </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>59034000</v>
+        <v>66455000</v>
       </c>
       <c r="AI3" t="n">
-        <v>40227000</v>
+        <v>48178000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>389000</v>
+        <v>1392000</v>
       </c>
       <c r="AL3" t="n">
-        <v>389000</v>
+        <v>1392000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>4015000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>4015000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>39838000</v>
+        <v>42771000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-29720000</v>
+        <v>-26704000</v>
       </c>
       <c r="AS3" t="n">
-        <v>69558000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>69475000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>4880000</v>
+        <v>4846000</v>
       </c>
       <c r="AV3" t="n">
         <v>64553000</v>
       </c>
       <c r="AW3" t="n">
-        <v>125000</v>
+        <v>76000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>18807000</v>
+        <v>18277000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>144000</v>
+        <v>222000</v>
       </c>
       <c r="BA3" t="n">
-        <v>491000</v>
+        <v>1972000</v>
       </c>
       <c r="BB3" t="n">
-        <v>323000</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>17849000</v>
+        <v>16083000</v>
       </c>
       <c r="BD3" t="n">
-        <v>16535000</v>
+        <v>13882000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1314000</v>
+        <v>2201000</v>
       </c>
       <c r="BF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1097703568</v>
@@ -1770,41 +1802,39 @@
       <c r="C4" t="n">
         <v>1097703568</v>
       </c>
-      <c r="D4" t="n">
-        <v>677000</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2890000</v>
+        <v>864000</v>
       </c>
       <c r="F4" t="n">
-        <v>61138000</v>
+        <v>57098000</v>
       </c>
       <c r="G4" t="n">
-        <v>64016000</v>
+        <v>57854000</v>
       </c>
       <c r="H4" t="n">
-        <v>14451000</v>
+        <v>16880000</v>
       </c>
       <c r="I4" t="n">
-        <v>61138000</v>
+        <v>57098000</v>
       </c>
       <c r="J4" t="n">
-        <v>12000</v>
+        <v>108000</v>
       </c>
       <c r="K4" t="n">
-        <v>61138000</v>
+        <v>57098000</v>
       </c>
       <c r="L4" t="n">
-        <v>61894000</v>
+        <v>57098000</v>
       </c>
       <c r="M4" t="n">
-        <v>61138000</v>
+        <v>57098000</v>
       </c>
       <c r="N4" t="n">
-        <v>61138000</v>
+        <v>57098000</v>
       </c>
       <c r="O4" t="n">
-        <v>9342000</v>
+        <v>6899000</v>
       </c>
       <c r="P4" t="n">
         <v>49101000</v>
@@ -1816,159 +1846,151 @@
         <v>1098000</v>
       </c>
       <c r="S4" t="n">
-        <v>5317000</v>
+        <v>1936000</v>
       </c>
       <c r="T4" t="n">
-        <v>1491000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>735000</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1927000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>735000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>855000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="AD4" t="n">
         <v>756000</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>756000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3826000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>2134000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2122000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>821000</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>66455000</v>
+        <v>59034000</v>
       </c>
       <c r="AI4" t="n">
-        <v>48178000</v>
+        <v>40227000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>1392000</v>
+        <v>389000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1392000</v>
+        <v>389000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>4015000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>4015000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>42771000</v>
+        <v>39838000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-26704000</v>
+        <v>-29720000</v>
       </c>
       <c r="AS4" t="n">
-        <v>69475000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>69558000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>4846000</v>
+        <v>4880000</v>
       </c>
       <c r="AV4" t="n">
         <v>64553000</v>
       </c>
       <c r="AW4" t="n">
-        <v>76000</v>
+        <v>125000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>18277000</v>
+        <v>18807000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>222000</v>
+        <v>144000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1972000</v>
+        <v>491000</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>323000</v>
       </c>
       <c r="BC4" t="n">
-        <v>16083000</v>
+        <v>17849000</v>
       </c>
       <c r="BD4" t="n">
-        <v>13882000</v>
+        <v>16535000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2201000</v>
+        <v>1314000</v>
       </c>
       <c r="BF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1097704000</v>
+        <v>1097703568</v>
       </c>
       <c r="C5" t="n">
-        <v>1097704000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2146000</v>
-      </c>
+        <v>1097703568</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>9938000</v>
+        <v>9000</v>
       </c>
       <c r="F5" t="n">
-        <v>61452000</v>
+        <v>58804000</v>
       </c>
       <c r="G5" t="n">
-        <v>71238000</v>
+        <v>58804000</v>
       </c>
       <c r="H5" t="n">
-        <v>7748000</v>
+        <v>18657000</v>
       </c>
       <c r="I5" t="n">
-        <v>61452000</v>
+        <v>58804000</v>
       </c>
       <c r="J5" t="n">
-        <v>152000</v>
+        <v>9000</v>
       </c>
       <c r="K5" t="n">
-        <v>61452000</v>
+        <v>58804000</v>
       </c>
       <c r="L5" t="n">
-        <v>66330000</v>
+        <v>58804000</v>
       </c>
       <c r="M5" t="n">
-        <v>61452000</v>
+        <v>58804000</v>
       </c>
       <c r="N5" t="n">
-        <v>61452000</v>
+        <v>58804000</v>
       </c>
       <c r="O5" t="n">
-        <v>8219000</v>
+        <v>8605000</v>
       </c>
       <c r="P5" t="n">
         <v>49101000</v>
@@ -1980,121 +2002,99 @@
         <v>1098000</v>
       </c>
       <c r="S5" t="n">
-        <v>10999000</v>
+        <v>1003000</v>
       </c>
       <c r="T5" t="n">
-        <v>5625000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>735000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>735000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>4890000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4878000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>5374000</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>1003000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>150000</v>
+      </c>
       <c r="AB5" t="n">
-        <v>5048000</v>
+        <v>9000</v>
       </c>
       <c r="AC5" t="n">
-        <v>140000</v>
+        <v>9000</v>
       </c>
       <c r="AD5" t="n">
-        <v>4908000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AG5" t="n">
-        <v>311000</v>
-      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>72451000</v>
+        <v>59807000</v>
       </c>
       <c r="AI5" t="n">
-        <v>59329000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>195000</v>
-      </c>
+        <v>40147000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>2731000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2731000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2731000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5167000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>5167000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8756000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>42675000</v>
+        <v>40147000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-23739000</v>
+        <v>-18339000</v>
       </c>
       <c r="AS5" t="n">
-        <v>66414000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>195000</v>
-      </c>
+        <v>58486000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>2025000</v>
+        <v>5753000</v>
       </c>
       <c r="AV5" t="n">
-        <v>64118000</v>
+        <v>52705000</v>
       </c>
       <c r="AW5" t="n">
-        <v>76000</v>
+        <v>28000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>13122000</v>
+        <v>19660000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>276000</v>
+        <v>154000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1392000</v>
+        <v>568000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>11454000</v>
+        <v>18938000</v>
       </c>
       <c r="BD5" t="n">
-        <v>3814000</v>
+        <v>14681000</v>
       </c>
       <c r="BE5" t="n">
-        <v>7640000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7640000</v>
-      </c>
+        <v>4257000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2319,462 +2319,462 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-10352000</v>
+        <v>4049000</v>
       </c>
       <c r="C2" t="n">
-        <v>-756000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-6089000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>317000</v>
+      </c>
       <c r="E2" t="n">
-        <v>-14559000</v>
+        <v>-201000</v>
       </c>
       <c r="F2" t="n">
-        <v>4257000</v>
+        <v>7640000</v>
       </c>
       <c r="G2" t="n">
-        <v>1314000</v>
+        <v>10032000</v>
       </c>
       <c r="H2" t="n">
-        <v>2943000</v>
+        <v>-2392000</v>
       </c>
       <c r="I2" t="n">
-        <v>-858000</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>-6441000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>317000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>317000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>317000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-756000</v>
+        <v>-6089000</v>
       </c>
       <c r="N2" t="n">
-        <v>-756000</v>
+        <v>-6089000</v>
       </c>
       <c r="O2" t="n">
-        <v>-756000</v>
+        <v>-6089000</v>
       </c>
       <c r="P2" t="n">
-        <v>-406000</v>
+        <v>-201000</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1854000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>244777000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-242923000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>12299000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1501000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-14559000</v>
+        <v>-201000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-14559000</v>
+        <v>-201000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4207000</v>
+        <v>4250000</v>
       </c>
       <c r="AC2" t="n">
-        <v>776000</v>
+        <v>638000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-31000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>-450000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>125000</v>
+        <v>-221000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-47000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-26000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-127000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>172000</v>
+        <v>-68000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-756000</v>
+        <v>-141000</v>
       </c>
       <c r="AK2" t="n">
-        <v>389000</v>
+        <v>5360000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2195000</v>
+        <v>1496000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2195000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-106000</v>
-      </c>
+        <v>1496000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>597000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>1706000</v>
+        <v>10488000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2406000</v>
+        <v>4206000</v>
       </c>
       <c r="C3" t="n">
-        <v>-2122000</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>-6908000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="n">
-        <v>-65000</v>
+        <v>-3185000</v>
       </c>
       <c r="F3" t="n">
-        <v>1314000</v>
+        <v>2201000</v>
       </c>
       <c r="G3" t="n">
-        <v>2201000</v>
+        <v>7640000</v>
       </c>
       <c r="H3" t="n">
-        <v>-887000</v>
+        <v>-5439000</v>
       </c>
       <c r="I3" t="n">
-        <v>-2227000</v>
+        <v>-7050000</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
-        <v>-2122000</v>
+        <v>-6908000</v>
       </c>
       <c r="N3" t="n">
-        <v>-2122000</v>
+        <v>-6908000</v>
       </c>
       <c r="O3" t="n">
-        <v>-2122000</v>
+        <v>-6908000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1131000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>-5780000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-32162000</v>
+      </c>
       <c r="R3" t="n">
-        <v>-2869000</v>
+        <v>-11168000</v>
       </c>
       <c r="S3" t="n">
-        <v>55220000</v>
+        <v>20994000</v>
       </c>
       <c r="T3" t="n">
-        <v>-58089000</v>
+        <v>-32162000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>8573000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8573000</v>
       </c>
       <c r="W3" t="n">
-        <v>1803000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1803000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-65000</v>
+        <v>-3185000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-65000</v>
+        <v>-3185000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2471000</v>
+        <v>7391000</v>
       </c>
       <c r="AC3" t="n">
-        <v>776000</v>
+        <v>425000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-190000</v>
+        <v>-351000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-983000</v>
+        <v>866000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1344000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>1373000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1287000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>361000</v>
+        <v>-507000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-488000</v>
+        <v>-189000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1250000</v>
+        <v>1493000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2142000</v>
+        <v>2292000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2142000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>2292000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>177000</v>
+      </c>
       <c r="AO3" t="n">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3974000</v>
+        <v>1123000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>4206000</v>
+        <v>2406000</v>
       </c>
       <c r="C4" t="n">
-        <v>-6908000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
+        <v>-2122000</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-3185000</v>
+        <v>-65000</v>
       </c>
       <c r="F4" t="n">
+        <v>1314000</v>
+      </c>
+      <c r="G4" t="n">
         <v>2201000</v>
       </c>
-      <c r="G4" t="n">
-        <v>7640000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-5439000</v>
+        <v>-887000</v>
       </c>
       <c r="I4" t="n">
-        <v>-7050000</v>
+        <v>-2227000</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-6908000</v>
+        <v>-2122000</v>
       </c>
       <c r="N4" t="n">
-        <v>-6908000</v>
+        <v>-2122000</v>
       </c>
       <c r="O4" t="n">
-        <v>-6908000</v>
+        <v>-2122000</v>
       </c>
       <c r="P4" t="n">
-        <v>-5780000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-32162000</v>
-      </c>
+        <v>-1131000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-11168000</v>
+        <v>-2869000</v>
       </c>
       <c r="S4" t="n">
-        <v>20994000</v>
+        <v>55220000</v>
       </c>
       <c r="T4" t="n">
-        <v>-32162000</v>
+        <v>-58089000</v>
       </c>
       <c r="U4" t="n">
-        <v>8573000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8573000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1803000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+        <v>1803000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="n">
-        <v>-3185000</v>
+        <v>-65000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3185000</v>
+        <v>-65000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7391000</v>
+        <v>2471000</v>
       </c>
       <c r="AC4" t="n">
-        <v>425000</v>
+        <v>776000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-351000</v>
+        <v>-190000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>866000</v>
+        <v>-983000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1373000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1287000</v>
-      </c>
+        <v>-1344000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-507000</v>
+        <v>361000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-189000</v>
+        <v>-488000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1493000</v>
+        <v>1250000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2292000</v>
+        <v>2142000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2292000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>177000</v>
-      </c>
+        <v>2142000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>2100000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1123000</v>
+        <v>-3974000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4049000</v>
+        <v>-10352000</v>
       </c>
       <c r="C5" t="n">
-        <v>-6089000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>317000</v>
-      </c>
+        <v>-756000</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-201000</v>
+        <v>-14559000</v>
       </c>
       <c r="F5" t="n">
-        <v>7640000</v>
+        <v>4257000</v>
       </c>
       <c r="G5" t="n">
-        <v>10032000</v>
+        <v>1314000</v>
       </c>
       <c r="H5" t="n">
-        <v>-2392000</v>
+        <v>2943000</v>
       </c>
       <c r="I5" t="n">
-        <v>-6441000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>317000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>317000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>317000</v>
-      </c>
+        <v>-858000</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-6089000</v>
+        <v>-756000</v>
       </c>
       <c r="N5" t="n">
-        <v>-6089000</v>
+        <v>-756000</v>
       </c>
       <c r="O5" t="n">
-        <v>-6089000</v>
+        <v>-756000</v>
       </c>
       <c r="P5" t="n">
-        <v>-201000</v>
+        <v>-406000</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1854000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>244777000</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+        <v>-242923000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>12299000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1501000</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-201000</v>
+        <v>-14559000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-201000</v>
+        <v>-14559000</v>
       </c>
       <c r="AB5" t="n">
-        <v>4250000</v>
+        <v>4207000</v>
       </c>
       <c r="AC5" t="n">
-        <v>638000</v>
+        <v>776000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-450000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>-31000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-221000</v>
+        <v>125000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-26000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-127000</v>
-      </c>
+        <v>-47000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-68000</v>
+        <v>172000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-141000</v>
+        <v>-756000</v>
       </c>
       <c r="AK5" t="n">
-        <v>5360000</v>
+        <v>389000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1496000</v>
+        <v>2195000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1496000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>597000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>2195000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>-106000</v>
+      </c>
       <c r="AP5" t="n">
-        <v>10488000</v>
+        <v>1706000</v>
       </c>
     </row>
   </sheetData>
@@ -3324,187 +3324,187 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Sainan  Liu', 'age': 41, 'title': 'Executive Chairlady of the Board', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 3071932, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Ha  Wu', 'age': 61, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1763226, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Suk Ching  Chan', 'age': 48, 'title': 'Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Sainan  Liu', 'age': 41, 'title': 'Executive Chairlady of the Board', 'yearBorn': 1984, 'fiscalYear': 2025, 'totalPay': 3072148, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Ha  Wu', 'age': 61, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1763351, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Suk Ching  Chan', 'age': 48, 'title': 'Company Secretary', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.146</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.149</v>
-      </c>
       <c r="Y2" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.146</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.149</v>
       </c>
       <c r="AC2" t="n">
         <v>1304467200</v>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.569</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AF2" t="n">
         <v>60000</v>
@@ -3646,19 +3646,19 @@
         <v>60000</v>
       </c>
       <c r="AH2" t="n">
-        <v>524550</v>
+        <v>374016</v>
       </c>
       <c r="AI2" t="n">
-        <v>116000</v>
+        <v>79400</v>
       </c>
       <c r="AJ2" t="n">
-        <v>116000</v>
+        <v>79400</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.153</v>
+        <v>0.146</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>163557840</v>
+        <v>160264720</v>
       </c>
       <c r="AP2" t="n">
         <v>160264720</v>
@@ -3676,7 +3676,7 @@
         <v>0.125</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.204</v>
+        <v>0.198</v>
       </c>
       <c r="AS2" t="n">
         <v>4.083333</v>
@@ -3685,13 +3685,13 @@
         <v>0.048</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.791542</v>
+        <v>8.614530999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.15346</v>
+        <v>0.15158</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.156935</v>
+        <v>0.15668</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>152555824</v>
+        <v>149262720</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.01919</v>
@@ -3729,10 +3729,10 @@
         <v>1097703568</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.4153377</v>
+        <v>0.41537026</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.35874423</v>
+        <v>0.35149363</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -3761,16 +3761,16 @@
         <v>1499299200</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.023</v>
       </c>
       <c r="BT2" t="n">
-        <v>46.955</v>
+        <v>45.941</v>
       </c>
       <c r="BU2" t="n">
         <v>-0.22751325</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.019722</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.149</v>
+        <v>0.146</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -3888,16 +3888,14 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>COURAGE INV</t>
         </is>
       </c>
       <c r="DD2" t="n">
-        <v>1780380989</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>-0.6802735</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.146</v>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
@@ -3932,94 +3930,96 @@
       </c>
       <c r="DM2" t="inlineStr">
         <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1781682760</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.005580008</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.036812294</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.010680005</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.068164445</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1308879000000</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.001000002</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>0.14 - 0.146</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>374016</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.020999998</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.16799998</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>0.125 - 0.198</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.26262626</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-22.751326</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1741345109</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1741345109</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
           <t>Courage Investment Group Limited</t>
         </is>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>2.0547988</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>COURAGE INV</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.003000006</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>0.149 - 0.149</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>524550</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.024000004</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.19200003</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>0.125 - 0.204</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.054999992</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.2696078</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-22.751326</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1741345109</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1741345109</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.004459992</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.029062897</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.007935002</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.05056235</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1308879000000</v>
+      <c r="EM2" t="b">
+        <v>0</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
